--- a/survey_templates/041_post_graduation_career_outcome_survey--survey_templates.xlsx
+++ b/survey_templates/041_post_graduation_career_outcome_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1106,8 +1106,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'option1':_'job_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'option1': 'Job 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'option2':_'job_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'option2': 'Job 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'option3':_'job_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'option3': 'Job 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'option1':_0}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'option1': 0}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'option2':_1}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'option2': 1}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'option3':_2}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'option3': 2}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'option4':_3}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'option4': 3}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'option5':_4}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'option5': 4}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'option6':_5}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'option6': 5}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'option1':_'industry_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'option1': 'Industry 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'option2':_'industry_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'option2': 'Industry 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'option3':_'industry_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'option3': 'Industry 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'option1':_'high_school'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'option1': 'High School'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'option2':_"bachelor's"}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'option2': "Bachelor's"}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'option3':_"master's"}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'option3': "Master's"}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'option4':_'doctoral'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'option4': 'Doctoral'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'option1':_'high_school'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'option1': 'High school'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'option2':_"bachelor's"}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'option2': "Bachelor's"}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'option3':_"master's"}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'option3': "Master's"}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'option4':_'doctoral'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'option4': 'Doctoral'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'option1':_'job_type_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'option1': 'Job Type 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'option2':_'job_type_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'option2': 'Job Type 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'option3':_'job_type_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'option3': 'Job Type 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'option1':_'job_sector_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'option1': 'Job Sector 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1543,12 +1543,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'option2':_'job_sector_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'option2': 'Job Sector 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1560,12 +1560,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'option3':_'job_sector_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'option3': 'Job Sector 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'option1':_'small'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'option1': 'Small'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1594,12 +1594,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'option2':_'medium'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'option2': 'Medium'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1611,12 +1611,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'option3':_'large'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'option3': 'Large'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1628,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'option1':_'job_classification_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'option1': 'Job Classification 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'option2':_'job_classification_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'option2': 'Job Classification 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1662,12 +1662,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'option3':_'job_classification_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'option3': 'Job Classification 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
